--- a/aReport_card/2025_2026/First_term/JSS3/First_term_JSS3_2025_2026.xlsx
+++ b/aReport_card/2025_2026/First_term/JSS3/First_term_JSS3_2025_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\aReport_card\2025_2026\First_term\JSS3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9C2DB4-D08D-4C19-8E8D-606A0B0839DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E028E54-0A19-4171-A180-25FED11361F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1941,7 +1941,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A2:A11 B1:AQ11" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:A11 B2:AQ11 B1:AN1 AQ1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>